--- a/brand-protection/2026-09-28/strike/04-bait.xlsx
+++ b/brand-protection/2026-09-28/strike/04-bait.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B62"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -427,6 +427,11 @@
           <t>Tags</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -439,6 +444,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -451,6 +461,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -463,6 +478,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -475,6 +495,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -487,6 +512,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -499,6 +529,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -511,6 +546,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -523,6 +563,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -535,6 +580,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -547,6 +597,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -559,6 +614,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -571,6 +631,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -583,6 +648,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -595,6 +665,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -607,6 +682,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -619,6 +699,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -631,6 +716,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -643,6 +733,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -655,6 +750,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -667,6 +767,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -679,6 +784,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -691,6 +801,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -703,6 +818,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -715,6 +835,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -727,6 +852,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -739,6 +869,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -751,6 +886,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -763,6 +903,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -775,6 +920,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -787,6 +937,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -799,6 +954,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -811,6 +971,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -823,6 +988,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -835,6 +1005,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -847,6 +1022,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -859,6 +1039,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -871,6 +1056,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -883,6 +1073,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -895,6 +1090,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -907,6 +1107,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -919,6 +1124,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -931,6 +1141,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -943,6 +1158,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -955,6 +1175,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -967,6 +1192,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -979,6 +1209,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -991,6 +1226,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1003,6 +1243,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1015,6 +1260,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1027,6 +1277,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1039,6 +1294,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1051,6 +1311,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1063,6 +1328,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1075,6 +1345,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1087,6 +1362,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1099,6 +1379,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1111,6 +1396,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1123,6 +1413,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1135,6 +1430,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1147,6 +1447,11 @@
           <t>strike-04-bait</t>
         </is>
       </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1157,6 +1462,11 @@
       <c r="B62" t="inlineStr">
         <is>
           <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
         </is>
       </c>
     </row>

--- a/brand-protection/2026-09-28/strike/04-bait.xlsx
+++ b/brand-protection/2026-09-28/strike/04-bait.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="sample" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,23 +413,73 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>URL</t>
+          <t>url</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Tags</t>
+          <t>label</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>website_category</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>phone_number</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>email_address</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>whatsapp</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>instagram</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>wechat</t>
         </is>
       </c>
     </row>
@@ -441,12 +491,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>24mostbet.click</t>
         </is>
       </c>
     </row>
@@ -458,12 +513,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>app-mostbet-uz.com</t>
         </is>
       </c>
     </row>
@@ -475,12 +540,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>az-casino-mostbet.com</t>
         </is>
       </c>
     </row>
@@ -492,12 +567,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>bestmostbet.com</t>
         </is>
       </c>
     </row>
@@ -509,12 +594,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>bwin-casino-bonuscode.buzz</t>
         </is>
       </c>
     </row>
@@ -526,12 +616,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>bwin-casino-enligne.buzz</t>
         </is>
       </c>
     </row>
@@ -543,12 +638,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>casino-mostbet-en.com</t>
         </is>
       </c>
     </row>
@@ -560,12 +665,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>casino-mostbet-pl.com</t>
         </is>
       </c>
     </row>
@@ -577,12 +692,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>casino-mostbet-play.com</t>
         </is>
       </c>
     </row>
@@ -594,12 +719,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>mostbet-0866.top</t>
         </is>
       </c>
     </row>
@@ -611,12 +741,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>mostbet-124.click</t>
         </is>
       </c>
     </row>
@@ -628,12 +763,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>mostbet-1534.team</t>
         </is>
       </c>
     </row>
@@ -645,12 +785,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>mostbet-apk-fr.com</t>
         </is>
       </c>
     </row>
@@ -662,12 +812,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>mostbet-app-fr.com</t>
         </is>
       </c>
     </row>
@@ -679,12 +839,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>mostbet-apps.com</t>
         </is>
       </c>
     </row>
@@ -696,12 +866,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>mostbet-bangladesh.com</t>
         </is>
       </c>
     </row>
@@ -713,12 +893,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>mostbet-brasil-cassino.com</t>
         </is>
       </c>
     </row>
@@ -730,12 +920,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>mostbet-brasil-top.com</t>
         </is>
       </c>
     </row>
@@ -747,12 +947,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>mostbet-brasil-win.com</t>
         </is>
       </c>
     </row>
@@ -764,12 +974,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>mostbet-canada.ca</t>
         </is>
       </c>
     </row>
@@ -781,12 +1001,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>mostbet-canada.net</t>
         </is>
       </c>
     </row>
@@ -798,12 +1023,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>mostbet-canada.org</t>
         </is>
       </c>
     </row>
@@ -815,12 +1045,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>mostbet-casino-brasil-br.com</t>
         </is>
       </c>
     </row>
@@ -832,12 +1072,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CZ</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>mostbet-casino-cz.cz</t>
         </is>
       </c>
     </row>
@@ -849,12 +1099,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>mostbet-casino-uz.site</t>
         </is>
       </c>
     </row>
@@ -866,12 +1121,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CZ</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>mostbet-casino.cz</t>
         </is>
       </c>
     </row>
@@ -883,12 +1148,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>mostbet-casino777.com</t>
         </is>
       </c>
     </row>
@@ -900,12 +1175,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>mostbet-cm.org</t>
         </is>
       </c>
     </row>
@@ -917,12 +1197,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CZ</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>mostbet-cz-login.cz</t>
         </is>
       </c>
     </row>
@@ -934,12 +1224,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>mostbet-download-free.ru</t>
         </is>
       </c>
     </row>
@@ -951,12 +1251,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>mostbet-gh.net</t>
         </is>
       </c>
     </row>
@@ -968,12 +1273,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>mostbet-guncel-giris.org</t>
         </is>
       </c>
     </row>
@@ -985,12 +1295,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>mostbet-ireland.org</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1317,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>KE</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>mostbet-ke.ke</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1344,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>mostbet-kenya.net</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1366,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>mostbet-luxury.com</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1393,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>mostbet-ng.org</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1415,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>mostbet-nigeria.net</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1437,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>mostbet-np.net</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1459,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>mostbet-online-ru.com</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1486,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>mostbet-online.bet</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1508,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>mostbet-philippines.org</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1530,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>mostbet-sn.net</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1552,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>mostbet-sportwetten.com</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1579,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>mostbet-tanzania.net</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1601,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>mostbet-uz-top.com</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1628,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>mostbet-uz.fun</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1650,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>mostbet-uz.su</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1672,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>mostbet.dev</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1694,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>mostbet.pics</t>
         </is>
       </c>
     </row>
@@ -1291,12 +1716,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>mostbet1-gr.com</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1743,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>mostbet4890.buzz</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1765,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>mostbetcasino1.pt</t>
         </is>
       </c>
     </row>
@@ -1342,12 +1792,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>mostbetclub.top</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1814,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>mostbetpk.site</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1836,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>mostbetru.net</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1858,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>mostbets.online</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1880,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>mostbets.world</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1902,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>mostbetsam.com</t>
         </is>
       </c>
     </row>
@@ -1444,12 +1929,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>mostbettur.top</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1951,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>strike-04-bait</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-04-bait</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>mostbetyukle.com</t>
         </is>
       </c>
     </row>
